--- a/data/trans_camb/MCS12_SP_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 6,79</t>
+          <t>-2,32; 6,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 9,06</t>
+          <t>-0,53; 8,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 4,89</t>
+          <t>-5,64; 4,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 14,66</t>
+          <t>7,66; 15,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 9,48</t>
+          <t>1,76; 10,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 9,73</t>
+          <t>2,14; 9,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 10,42</t>
+          <t>4,21; 10,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,09</t>
+          <t>1,71; 7,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 6,67</t>
+          <t>0,2; 6,13</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 13,89</t>
+          <t>-4,44; 13,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 18,27</t>
+          <t>-1,01; 16,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 9,78</t>
+          <t>-10,36; 8,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,91; 27,58</t>
+          <t>13,18; 27,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 17,3</t>
+          <t>3,05; 18,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 17,95</t>
+          <t>3,78; 18,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 19,72</t>
+          <t>7,57; 19,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,06; 15,25</t>
+          <t>3,24; 15,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 12,5</t>
+          <t>0,36; 11,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 11,61</t>
+          <t>4,78; 11,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 10,44</t>
+          <t>4,04; 10,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 1,84</t>
+          <t>-13,13; 2,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 10,06</t>
+          <t>3,27; 10,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 3,08</t>
+          <t>-3,42; 2,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 13,67</t>
+          <t>-6,61; 14,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,88</t>
+          <t>5,0; 9,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,99</t>
+          <t>1,4; 5,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 5,89</t>
+          <t>-8,82; 5,53</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,71; 31,7</t>
+          <t>11,67; 31,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,9; 28,14</t>
+          <t>10,0; 29,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 4,72</t>
+          <t>-34,25; 5,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 19,94</t>
+          <t>5,94; 19,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 5,99</t>
+          <t>-6,19; 5,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 25,9</t>
+          <t>-12,33; 27,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 22,24</t>
+          <t>10,67; 22,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 13,49</t>
+          <t>2,96; 13,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,23; 13,01</t>
+          <t>-18,99; 12,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 12,62</t>
+          <t>-0,28; 12,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 12,03</t>
+          <t>-0,55; 11,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 8,22</t>
+          <t>-5,03; 7,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 8,01</t>
+          <t>-6,0; 7,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,93; 4,04</t>
+          <t>-9,27; 3,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 0,63</t>
+          <t>-11,53; 0,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 8,68</t>
+          <t>-0,79; 8,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 6,46</t>
+          <t>-2,39; 6,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,87</t>
+          <t>-5,28; 2,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 34,37</t>
+          <t>-0,78; 35,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 33,42</t>
+          <t>-1,36; 31,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 22,82</t>
+          <t>-11,66; 21,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 16,12</t>
+          <t>-10,86; 15,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 8,09</t>
+          <t>-16,42; 7,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 1,24</t>
+          <t>-20,12; 0,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 19,91</t>
+          <t>-1,54; 20,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 14,85</t>
+          <t>-5,18; 15,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 6,46</t>
+          <t>-11,13; 6,42</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,23; 8,41</t>
+          <t>3,27; 8,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,43</t>
+          <t>2,48; 7,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -0,65</t>
+          <t>-13,69; -0,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 10,14</t>
+          <t>5,15; 10,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,11</t>
+          <t>-1,62; 3,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 8,39</t>
+          <t>-4,36; 8,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,45</t>
+          <t>4,96; 8,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,68</t>
+          <t>1,15; 4,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 1,82</t>
+          <t>-7,04; 2,38</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,23; 19,86</t>
+          <t>7,54; 19,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 17,61</t>
+          <t>5,54; 17,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,55; -1,57</t>
+          <t>-30,49; -1,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,1; 19,05</t>
+          <t>9,44; 19,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 5,83</t>
+          <t>-2,94; 6,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 15,68</t>
+          <t>-8,03; 15,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,87; 17,75</t>
+          <t>10,04; 17,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,75</t>
+          <t>2,31; 9,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 3,72</t>
+          <t>-14,41; 4,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R2-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-2,69</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,89</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>2,36</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,75</t>
+          <t>-2,68; 6,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 8,61</t>
+          <t>-0,9; 8,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 4,44</t>
+          <t>-7,72; 2,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,07</t>
+          <t>7,29; 14,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,04</t>
+          <t>1,48; 9,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,83</t>
+          <t>2,08; 9,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 10,09</t>
+          <t>4,19; 10,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,91</t>
+          <t>1,87; 8,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 6,13</t>
+          <t>-0,72; 5,45</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,25%</t>
+          <t>-5,12%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 13,68</t>
+          <t>-4,92; 12,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 16,93</t>
+          <t>-1,73; 17,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 8,8</t>
+          <t>-14,18; 4,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,18; 27,79</t>
+          <t>12,6; 27,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 18,62</t>
+          <t>2,55; 17,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 18,32</t>
+          <t>3,63; 18,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 19,0</t>
+          <t>7,5; 19,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 15,01</t>
+          <t>3,31; 15,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 11,49</t>
+          <t>-1,27; 10,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-3,85</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-5,67</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-2,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 11,5</t>
+          <t>5,1; 11,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,67</t>
+          <t>3,95; 10,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 2,15</t>
+          <t>-2,0; 4,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 10,03</t>
+          <t>3,32; 10,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,81</t>
+          <t>-3,71; 2,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 14,23</t>
+          <t>-8,85; -1,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 9,76</t>
+          <t>4,89; 9,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,85</t>
+          <t>1,07; 5,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 5,53</t>
+          <t>-4,69; -0,07</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-9,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>-10,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-3,91%</t>
+          <t>-4,58%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 31,02</t>
+          <t>12,17; 32,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,0; 29,0</t>
+          <t>9,66; 27,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 5,72</t>
+          <t>-4,9; 11,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,94; 19,88</t>
+          <t>6,02; 20,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 5,52</t>
+          <t>-6,86; 5,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 27,63</t>
+          <t>-16,14; -3,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 22,01</t>
+          <t>10,46; 22,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 13,28</t>
+          <t>2,29; 13,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 12,25</t>
+          <t>-9,81; -0,12</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>2,11</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,39</t>
+          <t>-4,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-0,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 12,67</t>
+          <t>-0,69; 12,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 11,43</t>
+          <t>-0,91; 12,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 7,87</t>
+          <t>-4,17; 7,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 7,59</t>
+          <t>-5,25; 8,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 3,59</t>
+          <t>-8,76; 3,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,53; 0,12</t>
+          <t>-9,85; 1,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 8,71</t>
+          <t>-1,01; 8,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 6,49</t>
+          <t>-2,17; 6,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 2,77</t>
+          <t>-4,38; 3,76</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-10,13%</t>
+          <t>-7,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-2,67%</t>
+          <t>-1,07%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 35,13</t>
+          <t>-1,67; 34,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 31,52</t>
+          <t>-2,27; 33,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 21,14</t>
+          <t>-9,59; 22,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 15,25</t>
+          <t>-9,37; 16,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 7,41</t>
+          <t>-15,6; 7,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 0,0</t>
+          <t>-17,21; 3,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 20,36</t>
+          <t>-2,13; 19,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 15,04</t>
+          <t>-4,57; 14,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 6,42</t>
+          <t>-9,05; 8,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-4,56</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-3,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,31</t>
+          <t>-2,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 8,14</t>
+          <t>3,23; 8,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,42</t>
+          <t>2,28; 7,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -0,62</t>
+          <t>-3,74; 1,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 10,09</t>
+          <t>5,13; 10,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,33</t>
+          <t>-1,8; 2,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 8,15</t>
+          <t>-5,72; -1,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,54</t>
+          <t>4,88; 8,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,63</t>
+          <t>1,03; 4,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 2,38</t>
+          <t>-3,97; -0,49</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,56%</t>
+          <t>-3,13%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,58%</t>
+          <t>-6,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-4,74%</t>
+          <t>-4,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,54; 19,42</t>
+          <t>7,17; 19,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,54; 17,6</t>
+          <t>5,16; 17,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,49; -1,5</t>
+          <t>-8,34; 2,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,44; 19,1</t>
+          <t>9,2; 18,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 6,32</t>
+          <t>-3,29; 5,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 15,42</t>
+          <t>-10,43; -2,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,04; 17,74</t>
+          <t>9,69; 17,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,31; 9,64</t>
+          <t>2,11; 9,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 4,93</t>
+          <t>-8,03; -1,0</t>
         </is>
       </c>
     </row>
